--- a/survey_templates/030_favorite_notification_feedback--survey_templates.xlsx
+++ b/survey_templates/030_favorite_notification_feedback--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,10 +437,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>favorite_notification_feedback</t>
+          <t>favorite_notification</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Favorite Notification Feedback</t>
+          <t>Favorite Notification</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>notification_type</t>
+          <t>Notification Type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>notification_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Notification Frequency</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>notification_source</t>
+          <t>notification_importance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>notification_source</t>
+          <t>Notification Importance</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>notification_frequency</t>
+          <t>notification_pain</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>notification_frequency</t>
+          <t>Notification Pain</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>notification_importance</t>
+          <t>notification_source</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>notification_importance</t>
+          <t>Notification Source</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>notification_pain</t>
+          <t>notification_channel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>notification_pain</t>
+          <t>Notification Channel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>favorite_notification</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>favorite_notification</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>Contact Info</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>notification_importance_level</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>Notification Importance Level</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>notification_pain_level</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>Notification Pain Level</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>notification_channel</t>
+          <t>notification_pain_importance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>notification_channel</t>
+          <t>Notification Pain Importance</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>notification_pain_source</t>
+          <t>notification_pain_importance_level</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>notification_pain_source</t>
+          <t>Notification Pain Importance Level</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>notification_pain_importance</t>
+          <t>notification_pain_frequency</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>notification_pain_importance</t>
+          <t>Notification Pain Frequency</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>notification_pain_frequency</t>
+          <t>notification_pain_source</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>notification_pain_frequency</t>
+          <t>Notification Pain Source</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,195 +893,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>notification_pain_channel</t>
+          <t>Notification Pain Channel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>notification_pain_importance_level</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>notification_pain_importance_level</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>notification_pain_level</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>notification_pain_level</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>notification_channel</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>notification_channel</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>notification_source</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>notification_source</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>notification_importance</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>notification_importance</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>notification_importance_level</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>notification_importance_level</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>notification_level</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>notification_level</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>notification_source_level</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>notification_source_level</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1199,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>in-app</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>in-app</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>in-app</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>in-app</t>
+          <t>text</t>
         </is>
       </c>
     </row>
@@ -1245,323 +1061,323 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>notification_source_choices</t>
+          <t>notification_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>notification_source_choices</t>
+          <t>notification_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>notification_source_choices</t>
+          <t>notification_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>notification_source_choices</t>
+          <t>notification_importance_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>notification_source_choices</t>
+          <t>notification_importance_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>somewhat</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>notification_source_choices</t>
+          <t>notification_importance_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>social media</t>
+          <t>very</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>notification_frequency_choices</t>
+          <t>notification_importance_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>not_much</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>not much</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>notification_frequency_choices</t>
+          <t>notification_pain_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>notification_frequency_choices</t>
+          <t>notification_pain_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>somewhat</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>notification_importance_choices</t>
+          <t>notification_pain_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>very</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>notification_importance_choices</t>
+          <t>notification_pain_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>not_much</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>not much</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>notification_importance_choices</t>
+          <t>notification_source_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>email</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>notification_importance_choices</t>
+          <t>notification_source_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_much</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>not_much</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>notification_pain_choices</t>
+          <t>notification_source_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>app</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>notification_pain_choices</t>
+          <t>notification_source_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>notification_pain_choices</t>
+          <t>notification_channel_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>email</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>notification_pain_choices</t>
+          <t>notification_channel_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>not_much</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>not_much</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>favorite_notification_choices</t>
+          <t>notification_channel_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>push</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>push</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>favorite_notification_choices</t>
+          <t>notification_channel_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>in-app</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>in-app</t>
         </is>
       </c>
     </row>
@@ -1573,165 +1389,165 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>notification_channel_choices</t>
+          <t>notification_importance_level_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>notification_channel_choices</t>
+          <t>notification_importance_level_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>somewhat</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>notification_channel_choices</t>
+          <t>notification_importance_level_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>in-app</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>in-app</t>
+          <t>very</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>notification_channel_choices</t>
+          <t>notification_importance_level_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>not_much</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>not much</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>notification_channel_choices</t>
+          <t>notification_pain_level_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>notification_pain_source_choices</t>
+          <t>notification_pain_level_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>somewhat</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>notification_pain_source_choices</t>
+          <t>notification_pain_level_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>very</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>notification_pain_source_choices</t>
+          <t>notification_pain_level_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>not_much</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>not much</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>notification_pain_source_choices</t>
+          <t>notification_pain_importance_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1559,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>somewhat</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1576,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>very</t>
         </is>
       </c>
     </row>
@@ -1777,726 +1593,284 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>not_much</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>not much</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>notification_pain_importance_choices</t>
+          <t>notification_pain_importance_level_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>not_much</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>not_much</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>notification_pain_frequency_choices</t>
+          <t>notification_pain_importance_level_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>somewhat</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>notification_pain_frequency_choices</t>
+          <t>notification_pain_importance_level_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>very</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>notification_pain_frequency_choices</t>
+          <t>notification_pain_importance_level_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>not_much</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>not much</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>notification_pain_channel_choices</t>
+          <t>notification_pain_frequency_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>notification_pain_channel_choices</t>
+          <t>notification_pain_frequency_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>notification_pain_channel_choices</t>
+          <t>notification_pain_frequency_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>notification_pain_channel_choices</t>
+          <t>notification_pain_source_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>email</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>notification_pain_importance_level_choices</t>
+          <t>notification_pain_source_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>notification_pain_importance_level_choices</t>
+          <t>notification_pain_source_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>app</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>app</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>notification_pain_importance_level_choices</t>
+          <t>notification_pain_source_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>notification_pain_importance_level_choices</t>
+          <t>notification_pain_channel_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>not_much</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>not_much</t>
+          <t>email</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>notification_pain_level_choices</t>
+          <t>notification_pain_channel_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>notification_pain_level_choices</t>
+          <t>notification_pain_channel_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>push</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>push</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>notification_pain_level_choices</t>
+          <t>notification_pain_channel_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>in-app</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>in-app</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>notification_pain_level_choices</t>
+          <t>notification_pain_channel_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>not_much</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>not_much</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>notification_channel_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>notification_channel_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>notification_channel_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>notification_channel_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>in-app</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>in-app</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>notification_channel_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>social_media</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>social_media</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>notification_channel_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>notification_source_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>notification_source_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>notification_source_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>app</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>notification_source_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>social_media</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>social_media</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>notification_importance_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>notification_importance_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>notification_importance_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>very</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>very</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>notification_importance_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>not_much</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>not_much</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>notification_importance_level_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>notification_importance_level_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>notification_importance_level_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>very</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>very</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>notification_importance_level_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>not_much</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>not_much</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>notification_level_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>notification_level_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>notification_level_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>very</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>very</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>notification_level_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>not_much</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>not_much</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>notification_source_level_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>notification_source_level_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>notification_source_level_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>very</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>very</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>notification_source_level_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>not_much</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>not_much</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
